--- a/artfynd/A 1202-2024 artfynd.xlsx
+++ b/artfynd/A 1202-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1202-2024 artfynd.xlsx
+++ b/artfynd/A 1202-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73885291</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422460.7604713197</v>
+        <v>422461</v>
       </c>
       <c r="R2" t="n">
-        <v>6474501.330339328</v>
+        <v>6474501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +753,9 @@
           <t>2008-04-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-04-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +789,7 @@
         <v>73885292</v>
       </c>
       <c r="B3" t="n">
-        <v>104490</v>
+        <v>106438</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422471.0005583157</v>
+        <v>422471</v>
       </c>
       <c r="R3" t="n">
-        <v>6474488.024351493</v>
+        <v>6474488</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +859,9 @@
           <t>2008-04-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-04-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +895,7 @@
         <v>73885294</v>
       </c>
       <c r="B4" t="n">
-        <v>108194</v>
+        <v>110137</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422443.6583497603</v>
+        <v>422444</v>
       </c>
       <c r="R4" t="n">
-        <v>6474433.002430371</v>
+        <v>6474433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,19 +965,9 @@
           <t>2010-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1001,7 @@
         <v>73885290</v>
       </c>
       <c r="B5" t="n">
-        <v>101120</v>
+        <v>102577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1068,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422491.8735847457</v>
+        <v>422492</v>
       </c>
       <c r="R5" t="n">
-        <v>6474481.322744112</v>
+        <v>6474481</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,19 +1071,9 @@
           <t>2008-04-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-04-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1107,7 @@
         <v>73885288</v>
       </c>
       <c r="B6" t="n">
-        <v>108194</v>
+        <v>110137</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422619.0434397002</v>
+        <v>422619</v>
       </c>
       <c r="R6" t="n">
-        <v>6474565.826605392</v>
+        <v>6474566</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1177,9 @@
           <t>2010-08-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-08-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,7 +1213,7 @@
         <v>73885293</v>
       </c>
       <c r="B7" t="n">
-        <v>96252</v>
+        <v>97997</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422441.8250689093</v>
+        <v>422442</v>
       </c>
       <c r="R7" t="n">
-        <v>6474419.934396329</v>
+        <v>6474420</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,19 +1287,9 @@
           <t>2010-08-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2010-08-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,7 +1323,7 @@
         <v>73885289</v>
       </c>
       <c r="B8" t="n">
-        <v>104490</v>
+        <v>106438</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1420,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422601.9469387167</v>
+        <v>422602</v>
       </c>
       <c r="R8" t="n">
-        <v>6474550.962905306</v>
+        <v>6474551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,19 +1393,9 @@
           <t>2008-04-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-04-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,7 +1429,7 @@
         <v>100427965</v>
       </c>
       <c r="B9" t="n">
-        <v>104490</v>
+        <v>106438</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422590.8927250362</v>
+        <v>422591</v>
       </c>
       <c r="R9" t="n">
-        <v>6474549.608158236</v>
+        <v>6474550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,19 +1513,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1549,7 @@
         <v>100427961</v>
       </c>
       <c r="B10" t="n">
-        <v>104490</v>
+        <v>106438</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1680,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422590.1731208766</v>
+        <v>422590</v>
       </c>
       <c r="R10" t="n">
-        <v>6474566.395131441</v>
+        <v>6474566</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,19 +1633,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1669,7 @@
         <v>100427956</v>
       </c>
       <c r="B11" t="n">
-        <v>108194</v>
+        <v>110137</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422633.5472872704</v>
+        <v>422634</v>
       </c>
       <c r="R11" t="n">
-        <v>6474609.045174645</v>
+        <v>6474609</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,19 +1739,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,7 +1775,7 @@
         <v>100428256</v>
       </c>
       <c r="B12" t="n">
-        <v>108194</v>
+        <v>110137</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1917,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>422609.6956386217</v>
+        <v>422610</v>
       </c>
       <c r="R12" t="n">
-        <v>6474517.78867743</v>
+        <v>6474518</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1950,19 +1850,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1996,7 +1886,7 @@
         <v>100427964</v>
       </c>
       <c r="B13" t="n">
-        <v>108194</v>
+        <v>110137</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>422590.8927250362</v>
+        <v>422591</v>
       </c>
       <c r="R13" t="n">
-        <v>6474549.608158236</v>
+        <v>6474550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,19 +1956,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,7 +1992,7 @@
         <v>100427955</v>
       </c>
       <c r="B14" t="n">
-        <v>104490</v>
+        <v>106438</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2163,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>422609.6956386217</v>
+        <v>422610</v>
       </c>
       <c r="R14" t="n">
-        <v>6474517.78867743</v>
+        <v>6474518</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,19 +2076,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 1202-2024 artfynd.xlsx
+++ b/artfynd/A 1202-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>73885294</v>
       </c>
       <c r="B4" t="n">
-        <v>110137</v>
+        <v>110140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>73885288</v>
       </c>
       <c r="B6" t="n">
-        <v>110137</v>
+        <v>110140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>100427956</v>
       </c>
       <c r="B11" t="n">
-        <v>110137</v>
+        <v>110140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>100428256</v>
       </c>
       <c r="B12" t="n">
-        <v>110137</v>
+        <v>110140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>100427964</v>
       </c>
       <c r="B13" t="n">
-        <v>110137</v>
+        <v>110140</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 1202-2024 artfynd.xlsx
+++ b/artfynd/A 1202-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>73885292</v>
       </c>
       <c r="B3" t="n">
-        <v>106438</v>
+        <v>106439</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>73885294</v>
       </c>
       <c r="B4" t="n">
-        <v>110140</v>
+        <v>110141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>73885288</v>
       </c>
       <c r="B6" t="n">
-        <v>110140</v>
+        <v>110141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>73885289</v>
       </c>
       <c r="B8" t="n">
-        <v>106438</v>
+        <v>106439</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>100427965</v>
       </c>
       <c r="B9" t="n">
-        <v>106438</v>
+        <v>106439</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>100427961</v>
       </c>
       <c r="B10" t="n">
-        <v>106438</v>
+        <v>106439</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>100427956</v>
       </c>
       <c r="B11" t="n">
-        <v>110140</v>
+        <v>110141</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>100428256</v>
       </c>
       <c r="B12" t="n">
-        <v>110140</v>
+        <v>110141</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>100427964</v>
       </c>
       <c r="B13" t="n">
-        <v>110140</v>
+        <v>110141</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>100427955</v>
       </c>
       <c r="B14" t="n">
-        <v>106438</v>
+        <v>106439</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 1202-2024 artfynd.xlsx
+++ b/artfynd/A 1202-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73885291</v>
+        <v>73885289</v>
       </c>
       <c r="B2" t="n">
-        <v>98123</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>219686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Backa, N om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422461</v>
+        <v>422602</v>
       </c>
       <c r="R2" t="n">
-        <v>6474501</v>
+        <v>6474551</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,12 +779,7 @@
         <v>73885292</v>
       </c>
       <c r="B3" t="n">
-        <v>106461</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73885294</v>
+        <v>100427953</v>
       </c>
       <c r="B4" t="n">
-        <v>110163</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,16 +888,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -925,17 +905,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Backa, N om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422444</v>
+        <v>422637</v>
       </c>
       <c r="R4" t="n">
-        <v>6474433</v>
+        <v>6474484</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-08-22</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-08-22</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,15 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73885290</v>
+        <v>100427955</v>
       </c>
       <c r="B5" t="n">
-        <v>102599</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,16 +1003,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222002</v>
+        <v>219686</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1031,17 +1020,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Backa, N om, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422492</v>
+        <v>422610</v>
       </c>
       <c r="R5" t="n">
-        <v>6474481</v>
+        <v>6474518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2008-04-14</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2008-04-14</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73885288</v>
+        <v>100427961</v>
       </c>
       <c r="B6" t="n">
-        <v>110163</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,16 +1118,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>219686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1137,14 +1135,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Backa, N om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422619</v>
+        <v>422590</v>
       </c>
       <c r="R6" t="n">
         <v>6474566</v>
@@ -1174,12 +1186,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-08-22</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-08-22</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,15 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73885293</v>
+        <v>100427965</v>
       </c>
       <c r="B7" t="n">
-        <v>98019</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,26 +1233,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>219686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1254,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422442</v>
+        <v>422591</v>
       </c>
       <c r="R7" t="n">
-        <v>6474420</v>
+        <v>6474550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,12 +1301,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-08-22</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-08-22</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,32 +1337,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73885289</v>
+        <v>73885288</v>
       </c>
       <c r="B8" t="n">
-        <v>106461</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219686</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1360,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422602</v>
+        <v>422619</v>
       </c>
       <c r="R8" t="n">
-        <v>6474551</v>
+        <v>6474566</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,12 +1402,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2008-04-14</t>
+          <t>2010-08-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2008-04-14</t>
+          <t>2010-08-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,32 +1438,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100427965</v>
+        <v>73885294</v>
       </c>
       <c r="B9" t="n">
-        <v>106461</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219686</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1459,31 +1466,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Backa, N om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422591</v>
+        <v>422444</v>
       </c>
       <c r="R9" t="n">
-        <v>6474550</v>
+        <v>6474433</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2010-08-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2010-08-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1539,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100427961</v>
+        <v>100427956</v>
       </c>
       <c r="B10" t="n">
-        <v>106461</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219686</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1579,31 +1567,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Backa, N om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422590</v>
+        <v>422634</v>
       </c>
       <c r="R10" t="n">
-        <v>6474566</v>
+        <v>6474609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,19 +1640,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100427956</v>
+        <v>100427964</v>
       </c>
       <c r="B11" t="n">
-        <v>110163</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1706,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422634</v>
+        <v>422591</v>
       </c>
       <c r="R11" t="n">
-        <v>6474609</v>
+        <v>6474550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,16 +1744,11 @@
         <v>100428256</v>
       </c>
       <c r="B12" t="n">
-        <v>110163</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1883,19 +1847,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100427964</v>
+        <v>114476280</v>
       </c>
       <c r="B13" t="n">
-        <v>110163</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1919,14 +1878,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Backa, N om, Vg</t>
+          <t>Noltorp syd, (Backa 4:3), Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>422591</v>
+        <v>422652</v>
       </c>
       <c r="R13" t="n">
-        <v>6474550</v>
+        <v>6474625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,12 +1912,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,35 +1928,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gles betad lövskog med graninslag</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karin Kjellberg</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karin Kjellberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100427955</v>
+        <v>73885291</v>
       </c>
       <c r="B14" t="n">
-        <v>106461</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,36 +1960,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219686</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2043,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>422610</v>
+        <v>422461</v>
       </c>
       <c r="R14" t="n">
-        <v>6474518</v>
+        <v>6474501</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,12 +2019,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2008-04-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2008-04-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,37 +2055,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114476250</v>
+        <v>114476261</v>
       </c>
       <c r="B15" t="n">
-        <v>101952</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>422593</v>
+        <v>422498</v>
       </c>
       <c r="R15" t="n">
-        <v>6474641</v>
+        <v>6474408</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,32 +2157,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114476261</v>
+        <v>73885290</v>
       </c>
       <c r="B16" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>222002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2252,17 +2188,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Noltorp syd, (Backa 4:3), Vg</t>
+          <t>Backa, N om, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>422498</v>
+        <v>422492</v>
       </c>
       <c r="R16" t="n">
-        <v>6474408</v>
+        <v>6474481</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2286,12 +2222,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2008-04-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2008-04-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,24 +2238,230 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gles betad lövskog med graninslag</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114476250</v>
+      </c>
+      <c r="B17" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Noltorp syd, (Backa 4:3), Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>422593</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6474641</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Varnhem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gles betad lövskog med graninslag</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>73885293</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Backa, N om, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>422442</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6474420</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Varnhem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2010-08-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2010-08-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1202-2024 artfynd.xlsx
+++ b/artfynd/A 1202-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885289</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885292</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100427953</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100427955</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100427961</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100427965</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885288</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885294</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100427956</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1738,6 +1788,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100427964</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100428256</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114476280</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885291</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2154,6 +2224,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114476261</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2255,6 +2330,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885290</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2357,6 +2437,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114476250</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2462,8 +2547,32 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885293</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>